--- a/table_2.xlsx
+++ b/table_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vlada\Desktop\научка\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F63E96-6C4D-4EB2-9A03-3B76D8D21910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A194FE-BC8E-47C7-90B9-0146D99E9538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25440" yWindow="3360" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -147,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -156,18 +156,32 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -176,15 +190,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -506,7 +526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="56">
+    <row r="3" spans="1:4" ht="42">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -520,7 +540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="56">
+    <row r="4" spans="1:4" ht="42">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -534,7 +554,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="56">
+    <row r="5" spans="1:4" ht="42">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -549,20 +569,21 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="56">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>